--- a/diseases/d001/2026-2029.xlsx
+++ b/diseases/d001/2026-2029.xlsx
@@ -12533,6 +12533,154 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12566,7 +12714,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -12649,7 +12797,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -12659,7 +12807,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d001/2026-2029.xlsx
+++ b/diseases/d001/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1061,9 +1058,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -2689,9 +2683,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -2837,9 +2828,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -4317,9 +4305,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -4465,9 +4450,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5945,9 +5927,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6093,9 +6072,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -7573,9 +7549,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -7721,9 +7694,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -9497,9 +9467,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -9645,9 +9612,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -9793,9 +9757,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -9941,9 +9902,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -10089,9 +10047,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10237,9 +10192,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -10385,9 +10337,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -10533,9 +10482,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -10681,9 +10627,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -10829,9 +10772,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -10977,9 +10917,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -11125,9 +11062,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -11273,9 +11207,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -11421,9 +11352,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -11569,9 +11497,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -11717,9 +11642,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -11865,9 +11787,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12013,9 +11932,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -12161,9 +12077,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -12309,9 +12222,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -12457,9 +12367,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -12603,9 +12510,6 @@
         <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">

--- a/diseases/d001/2026-2029.xlsx
+++ b/diseases/d001/2026-2029.xlsx
@@ -12585,6 +12585,151 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr"/>
+      <c r="AT83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12618,7 +12763,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -12701,7 +12846,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -12711,7 +12856,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d001/2026-2029.xlsx
+++ b/diseases/d001/2026-2029.xlsx
@@ -10873,12 +10873,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -10915,6 +10915,9 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
@@ -10951,42 +10954,42 @@
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -11018,12 +11021,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -11048,7 +11051,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -11096,42 +11099,42 @@
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -11163,12 +11166,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -11241,42 +11244,42 @@
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11308,12 +11311,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11338,7 +11341,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -11386,42 +11389,42 @@
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -11453,12 +11456,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -11531,42 +11534,42 @@
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11598,12 +11601,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -11628,7 +11631,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -11676,42 +11679,42 @@
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -11743,12 +11746,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -11821,42 +11824,42 @@
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11888,12 +11891,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -11918,7 +11921,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -11966,42 +11969,42 @@
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -12033,12 +12036,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -12111,42 +12114,42 @@
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12178,12 +12181,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -12208,7 +12211,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -12256,42 +12259,42 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -12323,12 +12326,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -12353,12 +12356,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -12401,42 +12404,42 @@
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12468,12 +12471,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -12498,7 +12501,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -12546,42 +12549,42 @@
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -12643,7 +12646,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -12725,6 +12728,151 @@
         </is>
       </c>
       <c r="BC83" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr"/>
+      <c r="AT84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV84" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -12846,7 +12994,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -12856,7 +13004,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d001/2026-2029.xlsx
+++ b/diseases/d001/2026-2029.xlsx
@@ -12878,6 +12878,151 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr"/>
+      <c r="AT85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12911,7 +13056,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12994,7 +13139,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -13004,7 +13149,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d001/2026-2029.xlsx
+++ b/diseases/d001/2026-2029.xlsx
@@ -21265,12 +21265,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21343,42 +21343,42 @@
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -21410,12 +21410,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -21488,42 +21488,42 @@
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -21555,12 +21555,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -21633,42 +21633,42 @@
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21700,12 +21700,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -21730,7 +21730,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -21744,9 +21744,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="P127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -21755,77 +21752,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21852,7 +21840,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -21904,98 +21892,18 @@
       <c r="P128" t="n">
         <v>0</v>
       </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD128" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE128" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF128" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG128" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN128" t="b">
-        <v>1</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -22089,17 +21997,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -22124,7 +22032,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -22138,76 +22046,168 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="R129" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>1</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
       <c r="AT129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -22239,12 +22239,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -22317,42 +22317,42 @@
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22384,12 +22384,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -22428,9 +22428,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="P131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -22439,77 +22436,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22536,7 +22524,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -22588,98 +22576,18 @@
       <c r="P132" t="n">
         <v>0</v>
       </c>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="W132" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X132" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="Y132" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD132" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE132" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF132" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG132" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN132" t="b">
-        <v>1</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -22773,17 +22681,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -22808,7 +22716,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -22822,76 +22730,168 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="R133" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN133" t="b">
+        <v>1</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
       <c r="AT133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -22923,12 +22923,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -23001,42 +23001,42 @@
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23068,12 +23068,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -23098,7 +23098,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -23112,9 +23112,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -23123,77 +23120,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ135" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23220,7 +23208,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -23272,98 +23260,18 @@
       <c r="P136" t="n">
         <v>0</v>
       </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD136" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE136" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF136" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG136" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN136" t="b">
-        <v>1</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
@@ -23457,17 +23365,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23492,7 +23400,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -23506,76 +23414,168 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="R137" t="n">
-        <v>0</v>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN137" t="b">
+        <v>1</v>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
       <c r="AT137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -23607,12 +23607,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -23685,42 +23685,42 @@
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23752,12 +23752,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -23782,7 +23782,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -23830,42 +23830,42 @@
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23897,12 +23897,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -23941,9 +23941,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="P140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -23952,77 +23949,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ140" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24049,7 +24037,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -24101,98 +24089,18 @@
       <c r="P141" t="n">
         <v>0</v>
       </c>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="V141" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="W141" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD141" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE141" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF141" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG141" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ141" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK141" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN141" t="b">
-        <v>1</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
@@ -24286,17 +24194,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -24321,12 +24229,12 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N142" t="n">
@@ -24335,76 +24243,168 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="R142" t="n">
-        <v>0</v>
-      </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN142" t="b">
+        <v>1</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
       <c r="AT142" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -24436,12 +24436,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24466,7 +24466,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -24514,42 +24514,42 @@
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24581,12 +24581,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24625,9 +24625,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="P144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -24636,77 +24633,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA144" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ144" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24733,7 +24721,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -24785,98 +24773,18 @@
       <c r="P145" t="n">
         <v>0</v>
       </c>
-      <c r="U145" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="V145" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="W145" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X145" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="Y145" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD145" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE145" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF145" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG145" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN145" t="b">
-        <v>1</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
@@ -24970,17 +24878,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -25005,7 +24913,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -25019,76 +24927,168 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="R146" t="n">
-        <v>0</v>
-      </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN146" t="b">
+        <v>1</v>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
       <c r="AT146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -25120,12 +25120,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -25164,9 +25164,6 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="P147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
@@ -25175,77 +25172,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA147" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ147" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25272,7 +25260,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -25324,98 +25312,18 @@
       <c r="P148" t="n">
         <v>0</v>
       </c>
-      <c r="U148" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="V148" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="W148" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD148" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE148" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF148" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG148" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM148" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN148" t="b">
-        <v>1</v>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
@@ -25509,17 +25417,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -25544,7 +25452,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -25558,76 +25466,168 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="R149" t="n">
-        <v>0</v>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN149" t="b">
+        <v>1</v>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
       <c r="AT149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -25659,12 +25659,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -25703,9 +25703,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="P150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -25714,77 +25711,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA150" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ150" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25811,7 +25799,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -25863,98 +25851,18 @@
       <c r="P151" t="n">
         <v>0</v>
       </c>
-      <c r="U151" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="V151" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PLAGUE</t>
-        </is>
-      </c>
-      <c r="W151" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>Plague</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD151" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE151" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF151" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG151" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN151" t="b">
-        <v>1</v>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
@@ -26020,6 +25928,243 @@
         </is>
       </c>
       <c r="BC151" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN152" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
+      <c r="AT152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA152" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC152" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -26141,7 +26286,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
@@ -26151,7 +26296,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d001/2026-2029.xlsx
+++ b/diseases/d001/2026-2029.xlsx
@@ -26170,6 +26170,690 @@
         </is>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr"/>
+      <c r="AT153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
+      <c r="AT154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN155" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PLAGUE; SER_SG_HIST_PLAGUE</t>
+        </is>
+      </c>
+      <c r="AT155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>plague</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr"/>
+      <c r="AT156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA156" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC156" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26203,7 +26887,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -26286,7 +26970,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10">
@@ -26296,7 +26980,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
@@ -26316,7 +27000,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
